--- a/RPGProject/Assets/Project/Data/ExcelData/ItemInfo.xlsx
+++ b/RPGProject/Assets/Project/Data/ExcelData/ItemInfo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\suyb1\Documents\GitHub\RPG\RPGProject\Assets\Project\Data\ExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C32F62D4-CAA7-4FFB-8C12-80DEE079CD6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A75AA5B7-1026-4918-BEB0-F237251BCB8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18510" yWindow="2295" windowWidth="19740" windowHeight="12075" xr2:uid="{3510F260-6A7D-4843-A2DA-E1BA315C89A0}"/>
+    <workbookView xWindow="13575" yWindow="2205" windowWidth="14790" windowHeight="10695" xr2:uid="{3510F260-6A7D-4843-A2DA-E1BA315C89A0}"/>
   </bookViews>
   <sheets>
     <sheet name="test" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="48">
   <si>
     <t>int</t>
   </si>
@@ -199,6 +199,17 @@
   <si>
     <t>작은 회복 알약</t>
     <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>박쥐의날개</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>거북이등껍질</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Material</t>
   </si>
 </sst>
 </file>
@@ -1179,7 +1190,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27433482-0B68-4763-85C6-CA814D549BDC}">
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
@@ -1826,6 +1837,82 @@
       </c>
       <c r="L17">
         <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" t="s">
+        <v>45</v>
+      </c>
+      <c r="D18" t="s">
+        <v>47</v>
+      </c>
+      <c r="E18" s="2">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>101</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+      <c r="I18" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J18" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="K18" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L18">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>16</v>
+      </c>
+      <c r="B19" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" t="s">
+        <v>46</v>
+      </c>
+      <c r="D19" t="s">
+        <v>47</v>
+      </c>
+      <c r="E19" s="2">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>102</v>
+      </c>
+      <c r="H19">
+        <v>1</v>
+      </c>
+      <c r="I19" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J19" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="K19" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L19">
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/RPGProject/Assets/Project/Data/ExcelData/ItemInfo.xlsx
+++ b/RPGProject/Assets/Project/Data/ExcelData/ItemInfo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\suyb1\Documents\GitHub\RPG\RPGProject\Assets\Project\Data\ExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A75AA5B7-1026-4918-BEB0-F237251BCB8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D579B145-BA2A-4D57-A520-408BD644A39C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13575" yWindow="2205" windowWidth="14790" windowHeight="10695" xr2:uid="{3510F260-6A7D-4843-A2DA-E1BA315C89A0}"/>
+    <workbookView xWindow="9075" yWindow="3780" windowWidth="14790" windowHeight="10695" xr2:uid="{3510F260-6A7D-4843-A2DA-E1BA315C89A0}"/>
   </bookViews>
   <sheets>
     <sheet name="test" sheetId="1" r:id="rId1"/>
